--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/PENNSYLVANIA_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/PENNSYLVANIA_2017.xlsx
@@ -1975,7 +1975,7 @@
         <v>56</v>
       </c>
       <c r="D90">
-        <v>0.009978617248752673</v>
+        <v>0.009978617248752672</v>
       </c>
     </row>
     <row r="91">
@@ -1993,7 +1993,7 @@
         <v>51</v>
       </c>
       <c r="D91">
-        <v>0.009087669280114041</v>
+        <v>0.009087669280114039</v>
       </c>
     </row>
     <row r="92">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C197">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C516">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C517">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C533">
